--- a/tests/fixtures/normal/_action_modified_smoke_test.xlsx
+++ b/tests/fixtures/normal/_action_modified_smoke_test.xlsx
@@ -435,7 +435,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
